--- a/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
+++ b/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\HPEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226829CA-22C7-4710-951B-DA08E09623C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878AE3F9-7A1A-456B-9BB1-9DE98075B5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26490" yWindow="1290" windowWidth="26130" windowHeight="14580" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="658" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="IEA Data" sheetId="2" r:id="rId2"/>
     <sheet name="Reformer data" sheetId="7" r:id="rId3"/>
     <sheet name="DoE Data" sheetId="6" r:id="rId4"/>
-    <sheet name="Conversion Factors" sheetId="4" r:id="rId5"/>
-    <sheet name="HPEC" sheetId="3" r:id="rId6"/>
-    <sheet name="HPEO" sheetId="5" r:id="rId7"/>
+    <sheet name="OM Split" sheetId="8" r:id="rId5"/>
+    <sheet name="Conversion Factors" sheetId="4" r:id="rId6"/>
+    <sheet name="HPEC" sheetId="3" r:id="rId7"/>
+    <sheet name="HPEO" sheetId="5" r:id="rId8"/>
+    <sheet name="HPVOS" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="btu_per_kwh">'Conversion Factors'!$A$3</definedName>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="259">
   <si>
     <t>HPEC Hydrogen Production Equipment CapEx</t>
   </si>
@@ -699,10 +701,178 @@
     <t>&lt;- resulting data</t>
   </si>
   <si>
-    <t>2022$/annual kg</t>
-  </si>
-  <si>
     <t>2012$/BTU</t>
+  </si>
+  <si>
+    <t>2022$ per annual kg of full-load (100% CF) capacity: $/kW x kWh/kg / 8760 h</t>
+  </si>
+  <si>
+    <t>2022$ per annual kg of full-load capacity, per year (fixed O&amp;M excl. stack replacement)</t>
+  </si>
+  <si>
+    <t>UTILIZATION AND STACK REPLACEMENT (added 2026-10-23)</t>
+  </si>
+  <si>
+    <t>CapEx and OpEx above are per unit of FULL-LOAD capacity. Utilization enters EPS only through hydgn/HPPECbP (= 1/CF - 1); keep the two CF cells below equal to the CFs used there.</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M excl. stack replacement, share of installed capex per year (DOE 24005)</t>
+  </si>
+  <si>
+    <t>Grid electrolysis capacity factor (DOE 24005 Table 2, Grid - Average Scenario)</t>
+  </si>
+  <si>
+    <t>Green electrolysis capacity factor: the utilization implied by the earlier derivation (106 MW / 0.51 CF for 18.25 Mkg/yr at 57.5 kWh/kg), kept so the green cost is unchanged</t>
+  </si>
+  <si>
+    <t>Grid electrolysis: year of operation</t>
+  </si>
+  <si>
+    <t>operating hours per year (8760 x CF)</t>
+  </si>
+  <si>
+    <t>cumulative operating hours</t>
+  </si>
+  <si>
+    <t>stack replacement this year (share of installed capex; 11% every 40,000 h)</t>
+  </si>
+  <si>
+    <t>discount factor (row 64)</t>
+  </si>
+  <si>
+    <t>levelized stack replacement, share of installed capex per year</t>
+  </si>
+  <si>
+    <t>Green electrolysis: year of operation</t>
+  </si>
+  <si>
+    <t>2026-10-23 update (bug B8 and stack replacement)</t>
+  </si>
+  <si>
+    <t>Electrolyzer CapEx was previously computed as 106 MW x $/kW / 0.51 CF / 18.25 Mkg, i.e. divided by a</t>
+  </si>
+  <si>
+    <t>capacity factor, while EPS also added HPPECbP excess capacity on the spending side - utilization was</t>
+  </si>
+  <si>
+    <t>counted twice and in two different ways. CapEx and OpEx are now on a full-load (100% CF) basis, as the</t>
+  </si>
+  <si>
+    <t>note above says: $/kW x 57.5 kWh/kg (DOE lifetime-average use) / 8760 h, the same 8760 h / kWh-per-kg</t>
+  </si>
+  <si>
+    <t>convention as hydgn/EHPpUC. Utilization is set only in hydgn/HPPECbP (= 1/CF - 1) and EPS applies</t>
+  </si>
+  <si>
+    <t>(1 + HPPECbP) to CapEx and OpEx in both the levelized cost and spending.</t>
+  </si>
+  <si>
+    <t>OpEx for electrolysis = 5% fixed O&amp;M + levelized stack replacement (11% of installed capex every</t>
+  </si>
+  <si>
+    <t>40,000 operating hours, DOE 24005), with replacement timing driven by each pathway's CF ('DoE Data'</t>
+  </si>
+  <si>
+    <t>rows 85-105, using the replacement and discounting assumptions in rows 46-64). Grid electrolysis</t>
+  </si>
+  <si>
+    <t>(97% CF) replaces stacks about every 4.7 years; green (CF in 'DoE Data'!B89) about every 8 years.</t>
+  </si>
+  <si>
+    <t>SMR CapEx/OpEx (Katebah et al., 500 t/d x 365 days) are already per unit of full-load capacity.</t>
+  </si>
+  <si>
+    <t>Fixed and variable O&amp;M by pathway (added 2026-10-23)</t>
+  </si>
+  <si>
+    <t>Source: NETL, Comparison of Commercial, State-of-the-Art, Fossil-Based Hydrogen Production Technologies, DOE/NETL-2022/3241 (2022), Exhibits 3-15 (Case 1 SMR) and 4-31 (Case 4 coal gasification), Dec 2018$</t>
+  </si>
+  <si>
+    <t>Purchased electricity is removed from NETL's variable O&amp;M because EPS charges electricity through FIoHP. Fuel is likewise charged through FIoHP.</t>
+  </si>
+  <si>
+    <t>NETL Case 1 SMR</t>
+  </si>
+  <si>
+    <t>NETL Case 4 coal gasification</t>
+  </si>
+  <si>
+    <t>Plant size (kg H2/day, full load)</t>
+  </si>
+  <si>
+    <t>Fixed operating costs ($/yr)</t>
+  </si>
+  <si>
+    <t>Variable operating costs total ($/kg H2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which purchased electricity ($/kg H2)</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M ($ per kg/yr of full-load capacity, 2018$)</t>
+  </si>
+  <si>
+    <t>Variable O&amp;M excl. electricity ($ per kg produced, 2018$)</t>
+  </si>
+  <si>
+    <t>HPEO = fixed + variable at full load ($ per kg/yr of capacity, 2018$)</t>
+  </si>
+  <si>
+    <t>HPEO (2012$ per BTU/yr of capacity)</t>
+  </si>
+  <si>
+    <t>Variable share of HPEO (HPVOS)</t>
+  </si>
+  <si>
+    <t>Electrolysis (DOE 24005): fixed O&amp;M = 5% of installed capex/yr; stack replacement is a variable cost (it scales with operating hours).</t>
+  </si>
+  <si>
+    <t>Stack replacement per unit produced at full load = levelized replacement share ('DoE Data' B97, B105) / CF ('DoE Data' B88, B89).</t>
+  </si>
+  <si>
+    <t>Grid electrolysis</t>
+  </si>
+  <si>
+    <t>Green electrolysis</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M share of capex per year</t>
+  </si>
+  <si>
+    <t>Stack replacement share of capex per unit of full-load output</t>
+  </si>
+  <si>
+    <t>Other pathways: biomass gasification uses coal gasification (as for capex); hydrocarbon partial oxidation uses SMR (85% of SMR cost, as for capex; NETL has no POx case); SMR with CCS uses SMR, with the CCS O&amp;M carried separately in CC CCS Total OM Cost per Hydrogen Sector Ton Sequestered.</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (share of HPEO that is variable)</t>
+  </si>
+  <si>
+    <t>share</t>
+  </si>
+  <si>
+    <t>2026-10-23 update (fixed vs variable O&amp;M)</t>
+  </si>
+  <si>
+    <t>HPEO is now fixed O&amp;M per unit of full-load capacity plus variable O&amp;M per unit produced at full load; HPVOS (new</t>
+  </si>
+  <si>
+    <t>export tab and CSV) is the variable share. EPS charges the fixed part per unit of capacity, (1 + HPPECbP) per unit</t>
+  </si>
+  <si>
+    <t>of output, and the variable part per unit of output; the dispatch cost keeps the variable part. Sources by pathway</t>
+  </si>
+  <si>
+    <t>are on the 'OM Split' tab. SMR, SMR+CCS and POx O&amp;M is re-levelled from Katebah et al. ('Reformer data' B36, which</t>
+  </si>
+  <si>
+    <t>appears to include utilities that EPS already charges through FIoHP) to NETL 2022 Case 1 without purchased power;</t>
+  </si>
+  <si>
+    <t>coal and biomass gasification to NETL Case 4. Electrolysis: DOE 24005 5% fixed O&amp;M plus stack replacement as a</t>
+  </si>
+  <si>
+    <t>variable cost (so electrolysis HPEO rises but its levelized cost is unchanged).</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="45.85546875" customWidth="1"/>
@@ -1621,6 +1791,106 @@
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +2069,7 @@
       </c>
       <c r="H6" s="11">
         <f>HPEC!H2*'IEA Data'!B21</f>
-        <v>25.319196660549348</v>
+        <v>14.592874254532326</v>
       </c>
       <c r="J6" s="18">
         <f>J5*usd_year_conv/'IEA Data'!$B$20</f>
@@ -1996,7 +2266,7 @@
       </c>
       <c r="D21" s="18">
         <f>HPEC!I2*'IEA Data'!B21</f>
-        <v>24.414939636958092</v>
+        <v>14.071700174013298</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2076,11 +2346,11 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <f>B32/B21</f>
-        <v>1.7132403345724911E-6</v>
+        <v>8.6767529440267494E-7</v>
       </c>
       <c r="B32" s="19">
         <f>HPEO!B3*B21*(1+B28)</f>
-        <v>0.31483921983877583</v>
+        <v>0.15945119155234291</v>
       </c>
       <c r="C32" t="s">
         <v>93</v>
@@ -2089,7 +2359,7 @@
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <f>SUM(A30:A32)</f>
-        <v>1.6364702521057188E-5</v>
+        <v>1.5519137480887374E-5</v>
       </c>
     </row>
   </sheetData>
@@ -2703,7 +2973,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F673B9B9-450F-45DB-9C6D-28B16550AAC5}">
-  <dimension ref="A17:AL83"/>
+  <dimension ref="A17:AL105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -2771,16 +3041,16 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="27">
-        <f>B23*$B$36/$B$43</f>
-        <v>415686274.50980389</v>
+        <f>B23*$B$36</f>
+        <v>212000000</v>
       </c>
       <c r="C24" s="27">
-        <f t="shared" ref="C24:D24" si="0">C23*$B$36/$B$43</f>
-        <v>323311546.8409586</v>
+        <f>C23*$B$36</f>
+        <v>164888888.8888889</v>
       </c>
       <c r="D24" s="27">
-        <f t="shared" si="0"/>
-        <v>207843137.25490195</v>
+        <f>D23*$B$36</f>
+        <v>106000000</v>
       </c>
       <c r="E24" t="s">
         <v>192</v>
@@ -2788,50 +3058,50 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="19">
-        <f>B24/$B$35</f>
-        <v>22.77733011012624</v>
+        <f>B23*$B$41/hours_per_year</f>
+        <v>13.127853881278538</v>
       </c>
       <c r="C25" s="19">
-        <f t="shared" ref="C25:D25" si="1">C24/$B$35</f>
-        <v>17.715701196764854</v>
+        <f>C23*$B$41/hours_per_year</f>
+        <v>10.210553018772197</v>
       </c>
       <c r="D25" s="19">
-        <f t="shared" si="1"/>
-        <v>11.38866505506312</v>
+        <f>D23*$B$41/hours_per_year</f>
+        <v>6.5639269406392691</v>
       </c>
       <c r="E25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <f>B25/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>1.328572068423011E-4</v>
+        <v>7.6573065853979578E-5</v>
       </c>
       <c r="C26" s="11">
         <f>C25/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>1.0333338309956757E-4</v>
+        <v>5.9556828997539679E-5</v>
       </c>
       <c r="D26" s="11">
         <f>D25/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>6.6428603421150552E-5</v>
+        <v>3.8286532926989789E-5</v>
       </c>
       <c r="E26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="27">
-        <f>B24*5%</f>
-        <v>20784313.725490198</v>
+        <f t="shared" ref="B27:D28" si="0">B24*$B$87</f>
+        <v>10600000</v>
       </c>
       <c r="C27" s="27">
-        <f t="shared" ref="C27:D27" si="2">C24*5%</f>
-        <v>16165577.34204793</v>
+        <f t="shared" si="0"/>
+        <v>8244444.444444445</v>
       </c>
       <c r="D27" s="27">
-        <f t="shared" si="2"/>
-        <v>10392156.862745099</v>
+        <f t="shared" si="0"/>
+        <v>5300000</v>
       </c>
       <c r="E27" t="s">
         <v>192</v>
@@ -2842,36 +3112,36 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="19">
-        <f>B27/$B$35</f>
-        <v>1.1388665055063123</v>
+        <f t="shared" si="0"/>
+        <v>0.65639269406392697</v>
       </c>
       <c r="C28" s="19">
-        <f t="shared" ref="C28" si="3">C27/$B$35</f>
-        <v>0.88578505983824274</v>
+        <f t="shared" si="0"/>
+        <v>0.51052765093860986</v>
       </c>
       <c r="D28" s="19">
-        <f t="shared" ref="D28" si="4">D27/$B$35</f>
-        <v>0.56943325275315615</v>
+        <f t="shared" si="0"/>
+        <v>0.32819634703196349</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="11">
         <f>B28/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>6.6428603421150575E-6</v>
+        <v>3.8286532926989791E-6</v>
       </c>
       <c r="C29" s="11">
         <f>C28/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>5.1666691549783778E-6</v>
+        <v>2.9778414498769836E-6</v>
       </c>
       <c r="D29" s="11">
         <f>D28/'IEA Data'!$B$18*'IEA Data'!$B$19*About!$A$72</f>
-        <v>3.3214301710575287E-6</v>
+        <v>1.9143266463494895E-6</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
@@ -2994,7 +3264,7 @@
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <f>B27/SUM(B64:AE64)/B53</f>
-        <v>0.10982736614928527</v>
+        <v>5.6011956736135488E-2</v>
       </c>
       <c r="B48" s="4">
         <f>0.11</f>
@@ -3122,119 +3392,119 @@
         <v>18250000</v>
       </c>
       <c r="C53">
-        <f t="shared" ref="C53:AE53" si="5">$B$35</f>
+        <f t="shared" ref="C53:AE53" si="1">$B$35</f>
         <v>18250000</v>
       </c>
       <c r="D53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="E53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="F53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="G53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="H53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="I53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="J53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="K53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="L53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="M53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="N53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="O53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="P53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="R53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="S53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="T53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="U53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="V53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="W53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="X53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="Y53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="Z53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="AA53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="AB53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="AC53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="AD53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
       <c r="AE53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>18250000</v>
       </c>
     </row>
@@ -3497,119 +3767,119 @@
         <v>34629375</v>
       </c>
       <c r="C56">
-        <f t="shared" ref="C56:AE56" si="6">$B$45*C53</f>
+        <f t="shared" ref="C56:AE56" si="2">$B$45*C53</f>
         <v>34629375</v>
       </c>
       <c r="D56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="E56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="F56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="G56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="H56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="I56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="J56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="K56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="L56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="M56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="N56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="O56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="P56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="R56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="S56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="T56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="U56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="V56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="W56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="X56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="Y56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="Z56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="AA56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="AB56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="AC56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="AD56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
       <c r="AE56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>34629375</v>
       </c>
     </row>
@@ -3631,119 +3901,119 @@
         <v>20784313.725490198</v>
       </c>
       <c r="C58" s="14">
-        <f t="shared" ref="C58:AE58" si="7">5%*$B$57</f>
+        <f t="shared" ref="C58:AE58" si="3">5%*$B$57</f>
         <v>20784313.725490198</v>
       </c>
       <c r="D58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="E58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="F58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="G58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="H58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="I58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="J58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="K58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="L58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="M58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="N58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="O58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="P58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="Q58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="R58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="S58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="T58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="U58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="V58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="W58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="X58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="Y58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="Z58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="AA58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="AB58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="AC58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="AD58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
       <c r="AE58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>20784313.725490198</v>
       </c>
     </row>
@@ -3753,119 +4023,119 @@
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14">
-        <f t="shared" ref="C59:AE59" si="8">IF(C55&lt;B55,$B$57*0.11,0)</f>
+        <f t="shared" ref="C59:AE59" si="4">IF(C55&lt;B55,$B$57*0.11,0)</f>
         <v>0</v>
       </c>
       <c r="D59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>45725490.196078427</v>
       </c>
       <c r="K59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>45725490.196078427</v>
       </c>
       <c r="T59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>45725490.196078427</v>
       </c>
       <c r="AC59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -3910,119 +4180,119 @@
         <v>471099963.2352941</v>
       </c>
       <c r="C61" s="14">
-        <f t="shared" ref="C61:AE61" si="9">SUM(C56:C59)/(1+$B$46)^(C52-1)</f>
+        <f t="shared" ref="C61:AE61" si="5">SUM(C56:C59)/(1+$B$46)^(C52-1)</f>
         <v>50376080.659536541</v>
       </c>
       <c r="D61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>45796436.963215031</v>
       </c>
       <c r="E61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>41633124.512013659</v>
       </c>
       <c r="F61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>37848295.010921508</v>
       </c>
       <c r="G61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>34407540.91901955</v>
       </c>
       <c r="H61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>31279582.653654136</v>
       </c>
       <c r="I61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>28435984.230594665</v>
       </c>
       <c r="J61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>47182173.395264447</v>
       </c>
       <c r="K61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>23500813.413714599</v>
       </c>
       <c r="L61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>21364375.830649633</v>
       </c>
       <c r="M61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>19422159.846045118</v>
       </c>
       <c r="N61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>17656508.950950108</v>
       </c>
       <c r="O61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>16051371.773591006</v>
       </c>
       <c r="P61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>14592156.157810003</v>
       </c>
       <c r="Q61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>13265596.507100003</v>
       </c>
       <c r="R61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>12059633.18827273</v>
       </c>
       <c r="S61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>20009847.366569262</v>
       </c>
       <c r="T61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>9966638.9985725023</v>
       </c>
       <c r="U61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>9060580.9077931829</v>
       </c>
       <c r="V61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>8236891.734357439</v>
       </c>
       <c r="W61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>7488083.3948703976</v>
       </c>
       <c r="X61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>6807348.5407912703</v>
       </c>
       <c r="Y61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>6188498.6734466087</v>
       </c>
       <c r="Z61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>5625907.884951463</v>
       </c>
       <c r="AA61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>5114461.7135922378</v>
       </c>
       <c r="AB61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>8486128.6121589579</v>
       </c>
       <c r="AC61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>4226827.8624729235</v>
       </c>
       <c r="AD61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3842570.7840662939</v>
       </c>
       <c r="AE61" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3493246.1673329943</v>
       </c>
     </row>
@@ -4035,119 +4305,119 @@
         <v>415686274.50980389</v>
       </c>
       <c r="C62">
-        <f t="shared" ref="C62:AE62" si="10">(C57+C59)/(1+$B$46)^(C52-1)</f>
+        <f t="shared" ref="C62:AE62" si="6">(C57+C59)/(1+$B$46)^(C52-1)</f>
         <v>0</v>
       </c>
       <c r="D62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>21331278.640178386</v>
       </c>
       <c r="K62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>9046544.4681395069</v>
       </c>
       <c r="T62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>3836617.9634387405</v>
       </c>
       <c r="AC62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4160,119 +4430,119 @@
         <v>20784313.725490198</v>
       </c>
       <c r="C63">
-        <f t="shared" ref="C63:AE63" si="11">C58/(1+$B$46)^(C52-1)</f>
+        <f t="shared" ref="C63:AE63" si="7">C58/(1+$B$46)^(C52-1)</f>
         <v>18894830.659536541</v>
       </c>
       <c r="D63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>17177118.781396855</v>
       </c>
       <c r="E63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>15615562.528542593</v>
       </c>
       <c r="F63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>14195965.935038721</v>
       </c>
       <c r="G63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>12905423.577307928</v>
       </c>
       <c r="H63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>11732203.252098115</v>
       </c>
       <c r="I63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>10665639.320089193</v>
       </c>
       <c r="J63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>9696035.7455356307</v>
       </c>
       <c r="K63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>8814577.9504869375</v>
       </c>
       <c r="L63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>8013252.6822608504</v>
       </c>
       <c r="M63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>7284775.1656916812</v>
       </c>
       <c r="N63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6622522.877901529</v>
       </c>
       <c r="O63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6020475.3435468441</v>
       </c>
       <c r="P63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>5473159.403224403</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4975599.4574767295</v>
       </c>
       <c r="R63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4523272.2340697544</v>
       </c>
       <c r="S63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4112065.6673361403</v>
       </c>
       <c r="T63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>3738241.515760127</v>
       </c>
       <c r="U63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>3398401.3779637511</v>
       </c>
       <c r="V63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>3089455.7981488649</v>
       </c>
       <c r="W63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2808596.1801353316</v>
       </c>
       <c r="X63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2553269.2546684826</v>
       </c>
       <c r="Y63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2321153.8678804385</v>
       </c>
       <c r="Z63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2110139.879891308</v>
       </c>
       <c r="AA63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1918308.9817193707</v>
       </c>
       <c r="AB63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1743917.2561085187</v>
       </c>
       <c r="AC63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1585379.3237350166</v>
       </c>
       <c r="AD63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1441253.9306681971</v>
       </c>
       <c r="AE63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1310230.8460619973</v>
       </c>
     </row>
@@ -4282,119 +4552,119 @@
         <v>1</v>
       </c>
       <c r="C64">
-        <f t="shared" ref="C64:AE64" si="12">1/((1+$B$46)^(C52-1))</f>
+        <f t="shared" ref="C64:AE64" si="8">1/((1+$B$46)^(C52-1))</f>
         <v>0.90909090909090906</v>
       </c>
       <c r="D64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.82644628099173545</v>
       </c>
       <c r="E64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.75131480090157754</v>
       </c>
       <c r="F64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.68301345536507052</v>
       </c>
       <c r="G64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.62092132305915493</v>
       </c>
       <c r="H64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.56447393005377722</v>
       </c>
       <c r="I64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.51315811823070645</v>
       </c>
       <c r="J64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.46650738020973315</v>
       </c>
       <c r="K64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.42409761837248466</v>
       </c>
       <c r="L64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.38554328942953148</v>
       </c>
       <c r="M64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.3504938994813922</v>
       </c>
       <c r="N64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.31863081771035656</v>
       </c>
       <c r="O64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.28966437973668779</v>
       </c>
       <c r="P64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.26333125430607973</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.23939204936916339</v>
       </c>
       <c r="R64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.21762913579014853</v>
       </c>
       <c r="S64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.19784466890013502</v>
       </c>
       <c r="T64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.17985878990921364</v>
       </c>
       <c r="U64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.16350799082655781</v>
       </c>
       <c r="V64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.14864362802414349</v>
       </c>
       <c r="W64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.13513057093103953</v>
       </c>
       <c r="X64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.12284597357367227</v>
       </c>
       <c r="Y64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.11167815779424752</v>
       </c>
       <c r="Z64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.10152559799477048</v>
       </c>
       <c r="AA64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>9.2295998177064048E-2</v>
       </c>
       <c r="AB64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>8.3905452888240042E-2</v>
       </c>
       <c r="AC64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>7.6277684443854576E-2</v>
       </c>
       <c r="AD64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>6.9343349494413245E-2</v>
       </c>
       <c r="AE64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>6.3039408631284766E-2</v>
       </c>
     </row>
@@ -4546,35 +4816,35 @@
         <v>54.545454545454547</v>
       </c>
       <c r="K78">
-        <f t="shared" ref="K78:R78" si="13">J78*K79/J79</f>
+        <f t="shared" ref="K78:R78" si="9">J78*K79/J79</f>
         <v>49.586776859504127</v>
       </c>
       <c r="L78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>45.078888054094648</v>
       </c>
       <c r="M78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>40.98080732190423</v>
       </c>
       <c r="N78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>37.255279383549293</v>
       </c>
       <c r="O78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>33.868435803226632</v>
       </c>
       <c r="P78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>30.789487093842389</v>
       </c>
       <c r="Q78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>27.990442812583989</v>
       </c>
       <c r="R78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>25.44585710234908</v>
       </c>
     </row>
@@ -4706,16 +4976,1319 @@
         <v>39.108663564660922</v>
       </c>
     </row>
-    <row r="82" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
       <c r="I82">
         <f>SUM(I79:R79)/SUM(I79:AL79)</f>
         <v>0.65181105941101536</v>
       </c>
     </row>
-    <row r="83" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="I83">
         <f>I82*I78</f>
         <v>39.108663564660922</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>206</v>
+      </c>
+      <c r="B87">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89">
+        <f>$B$43*$B$35*$B$41/($B$36*hours_per_year)</f>
+        <v>0.57635613207547165</v>
+      </c>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>209</v>
+      </c>
+      <c r="B92">
+        <f t="shared" ref="B92:AE92" si="10">B$52</f>
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="O92">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="P92">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="S92">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="T92">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="V92">
+        <f t="shared" si="10"/>
+        <v>21</v>
+      </c>
+      <c r="W92">
+        <f t="shared" si="10"/>
+        <v>22</v>
+      </c>
+      <c r="X92">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="Y92">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="Z92">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="AA92">
+        <f t="shared" si="10"/>
+        <v>26</v>
+      </c>
+      <c r="AB92">
+        <f t="shared" si="10"/>
+        <v>27</v>
+      </c>
+      <c r="AC92">
+        <f t="shared" si="10"/>
+        <v>28</v>
+      </c>
+      <c r="AD92">
+        <f t="shared" si="10"/>
+        <v>29</v>
+      </c>
+      <c r="AE92">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93">
+        <f t="shared" ref="B93:AE93" si="11">hours_per_year*$B$88</f>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="O93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="P93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="S93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="T93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="U93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="V93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="W93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="X93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="Y93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="Z93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="AA93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="AB93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="AC93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="AD93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="AE93">
+        <f t="shared" si="11"/>
+        <v>8497.1999999999989</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>211</v>
+      </c>
+      <c r="B94">
+        <f>SUM($B93:B93)</f>
+        <v>8497.1999999999989</v>
+      </c>
+      <c r="C94">
+        <f>SUM($B93:C93)</f>
+        <v>16994.399999999998</v>
+      </c>
+      <c r="D94">
+        <f>SUM($B93:D93)</f>
+        <v>25491.599999999999</v>
+      </c>
+      <c r="E94">
+        <f>SUM($B93:E93)</f>
+        <v>33988.799999999996</v>
+      </c>
+      <c r="F94">
+        <f>SUM($B93:F93)</f>
+        <v>42485.999999999993</v>
+      </c>
+      <c r="G94">
+        <f>SUM($B93:G93)</f>
+        <v>50983.19999999999</v>
+      </c>
+      <c r="H94">
+        <f>SUM($B93:H93)</f>
+        <v>59480.399999999987</v>
+      </c>
+      <c r="I94">
+        <f>SUM($B93:I93)</f>
+        <v>67977.599999999991</v>
+      </c>
+      <c r="J94">
+        <f>SUM($B93:J93)</f>
+        <v>76474.799999999988</v>
+      </c>
+      <c r="K94">
+        <f>SUM($B93:K93)</f>
+        <v>84971.999999999985</v>
+      </c>
+      <c r="L94">
+        <f>SUM($B93:L93)</f>
+        <v>93469.199999999983</v>
+      </c>
+      <c r="M94">
+        <f>SUM($B93:M93)</f>
+        <v>101966.39999999998</v>
+      </c>
+      <c r="N94">
+        <f>SUM($B93:N93)</f>
+        <v>110463.59999999998</v>
+      </c>
+      <c r="O94">
+        <f>SUM($B93:O93)</f>
+        <v>118960.79999999997</v>
+      </c>
+      <c r="P94">
+        <f>SUM($B93:P93)</f>
+        <v>127457.99999999997</v>
+      </c>
+      <c r="Q94">
+        <f>SUM($B93:Q93)</f>
+        <v>135955.19999999998</v>
+      </c>
+      <c r="R94">
+        <f>SUM($B93:R93)</f>
+        <v>144452.4</v>
+      </c>
+      <c r="S94">
+        <f>SUM($B93:S93)</f>
+        <v>152949.6</v>
+      </c>
+      <c r="T94">
+        <f>SUM($B93:T93)</f>
+        <v>161446.80000000002</v>
+      </c>
+      <c r="U94">
+        <f>SUM($B93:U93)</f>
+        <v>169944.00000000003</v>
+      </c>
+      <c r="V94">
+        <f>SUM($B93:V93)</f>
+        <v>178441.20000000004</v>
+      </c>
+      <c r="W94">
+        <f>SUM($B93:W93)</f>
+        <v>186938.40000000005</v>
+      </c>
+      <c r="X94">
+        <f>SUM($B93:X93)</f>
+        <v>195435.60000000006</v>
+      </c>
+      <c r="Y94">
+        <f>SUM($B93:Y93)</f>
+        <v>203932.80000000008</v>
+      </c>
+      <c r="Z94">
+        <f>SUM($B93:Z93)</f>
+        <v>212430.00000000009</v>
+      </c>
+      <c r="AA94">
+        <f>SUM($B93:AA93)</f>
+        <v>220927.2000000001</v>
+      </c>
+      <c r="AB94">
+        <f>SUM($B93:AB93)</f>
+        <v>229424.40000000011</v>
+      </c>
+      <c r="AC94">
+        <f>SUM($B93:AC93)</f>
+        <v>237921.60000000012</v>
+      </c>
+      <c r="AD94">
+        <f>SUM($B93:AD93)</f>
+        <v>246418.80000000013</v>
+      </c>
+      <c r="AE94">
+        <f>SUM($B93:AE93)</f>
+        <v>254916.00000000015</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95">
+        <f t="shared" ref="B95:AE95" si="12">IF(INT(B94/$B$49)&gt;INT((B94-B93)/$B$49),$B$48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="U95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Y95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="Z95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AA95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AB95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AD95">
+        <f t="shared" si="12"/>
+        <v>0.11</v>
+      </c>
+      <c r="AE95">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96">
+        <f t="shared" ref="B96:AE96" si="13">B$64</f>
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="13"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="13"/>
+        <v>0.82644628099173545</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="13"/>
+        <v>0.75131480090157754</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="13"/>
+        <v>0.68301345536507052</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="13"/>
+        <v>0.62092132305915493</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="13"/>
+        <v>0.56447393005377722</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="13"/>
+        <v>0.51315811823070645</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="13"/>
+        <v>0.46650738020973315</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="13"/>
+        <v>0.42409761837248466</v>
+      </c>
+      <c r="L96">
+        <f t="shared" si="13"/>
+        <v>0.38554328942953148</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="13"/>
+        <v>0.3504938994813922</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="13"/>
+        <v>0.31863081771035656</v>
+      </c>
+      <c r="O96">
+        <f t="shared" si="13"/>
+        <v>0.28966437973668779</v>
+      </c>
+      <c r="P96">
+        <f t="shared" si="13"/>
+        <v>0.26333125430607973</v>
+      </c>
+      <c r="Q96">
+        <f t="shared" si="13"/>
+        <v>0.23939204936916339</v>
+      </c>
+      <c r="R96">
+        <f t="shared" si="13"/>
+        <v>0.21762913579014853</v>
+      </c>
+      <c r="S96">
+        <f t="shared" si="13"/>
+        <v>0.19784466890013502</v>
+      </c>
+      <c r="T96">
+        <f t="shared" si="13"/>
+        <v>0.17985878990921364</v>
+      </c>
+      <c r="U96">
+        <f t="shared" si="13"/>
+        <v>0.16350799082655781</v>
+      </c>
+      <c r="V96">
+        <f t="shared" si="13"/>
+        <v>0.14864362802414349</v>
+      </c>
+      <c r="W96">
+        <f t="shared" si="13"/>
+        <v>0.13513057093103953</v>
+      </c>
+      <c r="X96">
+        <f t="shared" si="13"/>
+        <v>0.12284597357367227</v>
+      </c>
+      <c r="Y96">
+        <f t="shared" si="13"/>
+        <v>0.11167815779424752</v>
+      </c>
+      <c r="Z96">
+        <f t="shared" si="13"/>
+        <v>0.10152559799477048</v>
+      </c>
+      <c r="AA96">
+        <f t="shared" si="13"/>
+        <v>9.2295998177064048E-2</v>
+      </c>
+      <c r="AB96">
+        <f t="shared" si="13"/>
+        <v>8.3905452888240042E-2</v>
+      </c>
+      <c r="AC96">
+        <f t="shared" si="13"/>
+        <v>7.6277684443854576E-2</v>
+      </c>
+      <c r="AD96">
+        <f t="shared" si="13"/>
+        <v>6.9343349494413245E-2</v>
+      </c>
+      <c r="AE96">
+        <f t="shared" si="13"/>
+        <v>6.3039408631284766E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97">
+        <f>SUMPRODUCT(B95:AE95,B96:AE96)/SUM(B96:AE96)</f>
+        <v>1.83657402568396E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100">
+        <f t="shared" ref="B100:AE100" si="14">B$52</f>
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="14"/>
+        <v>7</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="N100">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="O100">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+      <c r="P100">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="14"/>
+        <v>16</v>
+      </c>
+      <c r="R100">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="S100">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="T100">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="U100">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="V100">
+        <f t="shared" si="14"/>
+        <v>21</v>
+      </c>
+      <c r="W100">
+        <f t="shared" si="14"/>
+        <v>22</v>
+      </c>
+      <c r="X100">
+        <f t="shared" si="14"/>
+        <v>23</v>
+      </c>
+      <c r="Y100">
+        <f t="shared" si="14"/>
+        <v>24</v>
+      </c>
+      <c r="Z100">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="AA100">
+        <f t="shared" si="14"/>
+        <v>26</v>
+      </c>
+      <c r="AB100">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="AC100">
+        <f t="shared" si="14"/>
+        <v>28</v>
+      </c>
+      <c r="AD100">
+        <f t="shared" si="14"/>
+        <v>29</v>
+      </c>
+      <c r="AE100">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101">
+        <f t="shared" ref="B101:AE101" si="15">hours_per_year*$B$89</f>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="L101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="N101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="O101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="P101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="R101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="S101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="T101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="U101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="V101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="W101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="X101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="Y101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="Z101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="AA101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="AB101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="AC101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="AD101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="AE101">
+        <f t="shared" si="15"/>
+        <v>5048.8797169811314</v>
+      </c>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102">
+        <f>SUM($B101:B101)</f>
+        <v>5048.8797169811314</v>
+      </c>
+      <c r="C102">
+        <f>SUM($B101:C101)</f>
+        <v>10097.759433962263</v>
+      </c>
+      <c r="D102">
+        <f>SUM($B101:D101)</f>
+        <v>15146.639150943394</v>
+      </c>
+      <c r="E102">
+        <f>SUM($B101:E101)</f>
+        <v>20195.518867924526</v>
+      </c>
+      <c r="F102">
+        <f>SUM($B101:F101)</f>
+        <v>25244.398584905655</v>
+      </c>
+      <c r="G102">
+        <f>SUM($B101:G101)</f>
+        <v>30293.278301886785</v>
+      </c>
+      <c r="H102">
+        <f>SUM($B101:H101)</f>
+        <v>35342.158018867915</v>
+      </c>
+      <c r="I102">
+        <f>SUM($B101:I101)</f>
+        <v>40391.037735849044</v>
+      </c>
+      <c r="J102">
+        <f>SUM($B101:J101)</f>
+        <v>45439.917452830174</v>
+      </c>
+      <c r="K102">
+        <f>SUM($B101:K101)</f>
+        <v>50488.797169811303</v>
+      </c>
+      <c r="L102">
+        <f>SUM($B101:L101)</f>
+        <v>55537.676886792433</v>
+      </c>
+      <c r="M102">
+        <f>SUM($B101:M101)</f>
+        <v>60586.556603773563</v>
+      </c>
+      <c r="N102">
+        <f>SUM($B101:N101)</f>
+        <v>65635.436320754699</v>
+      </c>
+      <c r="O102">
+        <f>SUM($B101:O101)</f>
+        <v>70684.316037735829</v>
+      </c>
+      <c r="P102">
+        <f>SUM($B101:P101)</f>
+        <v>75733.195754716959</v>
+      </c>
+      <c r="Q102">
+        <f>SUM($B101:Q101)</f>
+        <v>80782.075471698088</v>
+      </c>
+      <c r="R102">
+        <f>SUM($B101:R101)</f>
+        <v>85830.955188679218</v>
+      </c>
+      <c r="S102">
+        <f>SUM($B101:S101)</f>
+        <v>90879.834905660347</v>
+      </c>
+      <c r="T102">
+        <f>SUM($B101:T101)</f>
+        <v>95928.714622641477</v>
+      </c>
+      <c r="U102">
+        <f>SUM($B101:U101)</f>
+        <v>100977.59433962261</v>
+      </c>
+      <c r="V102">
+        <f>SUM($B101:V101)</f>
+        <v>106026.47405660374</v>
+      </c>
+      <c r="W102">
+        <f>SUM($B101:W101)</f>
+        <v>111075.35377358487</v>
+      </c>
+      <c r="X102">
+        <f>SUM($B101:X101)</f>
+        <v>116124.233490566</v>
+      </c>
+      <c r="Y102">
+        <f>SUM($B101:Y101)</f>
+        <v>121173.11320754713</v>
+      </c>
+      <c r="Z102">
+        <f>SUM($B101:Z101)</f>
+        <v>126221.99292452825</v>
+      </c>
+      <c r="AA102">
+        <f>SUM($B101:AA101)</f>
+        <v>131270.8726415094</v>
+      </c>
+      <c r="AB102">
+        <f>SUM($B101:AB101)</f>
+        <v>136319.75235849054</v>
+      </c>
+      <c r="AC102">
+        <f>SUM($B101:AC101)</f>
+        <v>141368.63207547169</v>
+      </c>
+      <c r="AD102">
+        <f>SUM($B101:AD101)</f>
+        <v>146417.51179245283</v>
+      </c>
+      <c r="AE102">
+        <f>SUM($B101:AE101)</f>
+        <v>151466.39150943398</v>
+      </c>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>212</v>
+      </c>
+      <c r="B103">
+        <f t="shared" ref="B103:AE103" si="16">IF(INT(B102/$B$49)&gt;INT((B102-B101)/$B$49),$B$48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="16"/>
+        <v>0.11</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="16"/>
+        <v>0.11</v>
+      </c>
+      <c r="R103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Y103">
+        <f t="shared" si="16"/>
+        <v>0.11</v>
+      </c>
+      <c r="Z103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AA103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AB103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AD103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AE103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>213</v>
+      </c>
+      <c r="B104">
+        <f t="shared" ref="B104:AE104" si="17">B$64</f>
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="17"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="17"/>
+        <v>0.82644628099173545</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="17"/>
+        <v>0.75131480090157754</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="17"/>
+        <v>0.68301345536507052</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="17"/>
+        <v>0.62092132305915493</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="17"/>
+        <v>0.56447393005377722</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="17"/>
+        <v>0.51315811823070645</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="17"/>
+        <v>0.46650738020973315</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="17"/>
+        <v>0.42409761837248466</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="17"/>
+        <v>0.38554328942953148</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="17"/>
+        <v>0.3504938994813922</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="17"/>
+        <v>0.31863081771035656</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="17"/>
+        <v>0.28966437973668779</v>
+      </c>
+      <c r="P104">
+        <f t="shared" si="17"/>
+        <v>0.26333125430607973</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="17"/>
+        <v>0.23939204936916339</v>
+      </c>
+      <c r="R104">
+        <f t="shared" si="17"/>
+        <v>0.21762913579014853</v>
+      </c>
+      <c r="S104">
+        <f t="shared" si="17"/>
+        <v>0.19784466890013502</v>
+      </c>
+      <c r="T104">
+        <f t="shared" si="17"/>
+        <v>0.17985878990921364</v>
+      </c>
+      <c r="U104">
+        <f t="shared" si="17"/>
+        <v>0.16350799082655781</v>
+      </c>
+      <c r="V104">
+        <f t="shared" si="17"/>
+        <v>0.14864362802414349</v>
+      </c>
+      <c r="W104">
+        <f t="shared" si="17"/>
+        <v>0.13513057093103953</v>
+      </c>
+      <c r="X104">
+        <f t="shared" si="17"/>
+        <v>0.12284597357367227</v>
+      </c>
+      <c r="Y104">
+        <f t="shared" si="17"/>
+        <v>0.11167815779424752</v>
+      </c>
+      <c r="Z104">
+        <f t="shared" si="17"/>
+        <v>0.10152559799477048</v>
+      </c>
+      <c r="AA104">
+        <f t="shared" si="17"/>
+        <v>9.2295998177064048E-2</v>
+      </c>
+      <c r="AB104">
+        <f t="shared" si="17"/>
+        <v>8.3905452888240042E-2</v>
+      </c>
+      <c r="AC104">
+        <f t="shared" si="17"/>
+        <v>7.6277684443854576E-2</v>
+      </c>
+      <c r="AD104">
+        <f t="shared" si="17"/>
+        <v>6.9343349494413245E-2</v>
+      </c>
+      <c r="AE104">
+        <f t="shared" si="17"/>
+        <v>6.3039408631284766E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>214</v>
+      </c>
+      <c r="B105">
+        <f>SUMPRODUCT(B103:AE103,B104:AE104)/SUM(B104:AE104)</f>
+        <v>9.1676691076440688E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4725,6 +6298,210 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DAB445-FD14-4067-BC3A-D5370D9E427C}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6">
+        <v>483014</v>
+      </c>
+      <c r="C6">
+        <v>659947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7">
+        <v>10633798</v>
+      </c>
+      <c r="C7">
+        <v>101984658</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="C8">
+        <v>0.43269000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9">
+        <v>4.5069999999999999E-2</v>
+      </c>
+      <c r="C9">
+        <v>6.5159999999999996E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10">
+        <f>B7/(B6*365)</f>
+        <v>6.0316456977820378E-2</v>
+      </c>
+      <c r="C10">
+        <f>C7/(C6*365)</f>
+        <v>0.42338251695637408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11">
+        <f>B8-B9</f>
+        <v>4.1830000000000006E-2</v>
+      </c>
+      <c r="C11">
+        <f>C8-C9</f>
+        <v>0.36753000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12">
+        <f>B10+B11</f>
+        <v>0.10214645697782038</v>
+      </c>
+      <c r="C12">
+        <f>C10+C11</f>
+        <v>0.7909125169563741</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13">
+        <f>B12*About!$A$75/'IEA Data'!$B$18*'IEA Data'!$B$19</f>
+        <v>6.9414023552214001E-7</v>
+      </c>
+      <c r="C13">
+        <f>C12*About!$A$75/'IEA Data'!$B$18*'IEA Data'!$B$19</f>
+        <v>5.3746768810269592E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14">
+        <f>B11/B12</f>
+        <v>0.40951004310489969</v>
+      </c>
+      <c r="C14">
+        <f>C11/C12</f>
+        <v>0.46469109050688168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20">
+        <f>'DoE Data'!$B$87</f>
+        <v>0.05</v>
+      </c>
+      <c r="C20">
+        <f>'DoE Data'!$B$87</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21">
+        <f>'DoE Data'!$B$97/'DoE Data'!$B$88</f>
+        <v>1.8933752842102681E-2</v>
+      </c>
+      <c r="C21">
+        <f>'DoE Data'!$B$105/'DoE Data'!$B$89</f>
+        <v>1.5906257602623368E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22">
+        <f>B21/(B20+B21)</f>
+        <v>0.27466592288209951</v>
+      </c>
+      <c r="C22">
+        <f>C21/(C20+C21)</f>
+        <v>0.24134669728220506</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4759,7 +6536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -4885,139 +6662,139 @@
       </c>
       <c r="B2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,B$1)</f>
-        <v>1.6730166787549267E-4</v>
+        <v>9.642534218649336E-5</v>
       </c>
       <c r="C2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,C$1)</f>
-        <v>1.6238103058503588E-4</v>
+        <v>9.3589302710419923E-5</v>
       </c>
       <c r="D2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,D$1)</f>
-        <v>1.5746039329458082E-4</v>
+        <v>9.0753263234346487E-5</v>
       </c>
       <c r="E2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,E$1)</f>
-        <v>1.5253975600412577E-4</v>
+        <v>8.7917223758273051E-5</v>
       </c>
       <c r="F2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,F$1)</f>
-        <v>1.4761911871366898E-4</v>
+        <v>8.5081184282199615E-5</v>
       </c>
       <c r="G2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,G$1)</f>
-        <v>1.4269848142321392E-4</v>
+        <v>8.2245144806126179E-5</v>
       </c>
       <c r="H2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,H$1)</f>
-        <v>1.3777784413275887E-4</v>
+        <v>7.940910533005361E-5</v>
       </c>
       <c r="I2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,I$1)</f>
-        <v>1.3285720684230208E-4</v>
+        <v>7.6573065853980174E-5</v>
       </c>
       <c r="J2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,J$1)</f>
-        <v>1.2793656955184703E-4</v>
+        <v>7.3737026377906738E-5</v>
       </c>
       <c r="K2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,K$1)</f>
-        <v>1.2301593226139197E-4</v>
+        <v>7.0900986901833302E-5</v>
       </c>
       <c r="L2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,L$1)</f>
-        <v>1.1809529497093518E-4</v>
+        <v>6.8064947425759866E-5</v>
       </c>
       <c r="M2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,M$1)</f>
-        <v>1.1317465768048013E-4</v>
+        <v>6.5228907949686429E-5</v>
       </c>
       <c r="N2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,N$1)</f>
-        <v>1.0825402039002507E-4</v>
+        <v>6.2392868473612993E-5</v>
       </c>
       <c r="O2" s="11">
         <f>TREND('DoE Data'!$B$26:$C$26,'DoE Data'!$B$22:$C$22,O$1)</f>
-        <v>1.0333338309957002E-4</v>
+        <v>5.9556828997540424E-5</v>
       </c>
       <c r="P2" s="13">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,P$1)</f>
-        <v>1.0148814411564677E-4</v>
+        <v>5.8493314194012561E-5</v>
       </c>
       <c r="Q2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,Q$1)</f>
-        <v>9.9642905131726127E-5</v>
+        <v>5.7429799390484697E-5</v>
       </c>
       <c r="R2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,R$1)</f>
-        <v>9.7797666147805048E-5</v>
+        <v>5.6366284586957267E-5</v>
       </c>
       <c r="S2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,S$1)</f>
-        <v>9.5952427163884402E-5</v>
+        <v>5.5302769783429837E-5</v>
       </c>
       <c r="T2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,T$1)</f>
-        <v>9.4107188179963323E-5</v>
+        <v>5.4239254979902406E-5</v>
       </c>
       <c r="U2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,U$1)</f>
-        <v>9.2261949196042678E-5</v>
+        <v>5.3175740176374976E-5</v>
       </c>
       <c r="V2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,V$1)</f>
-        <v>9.0416710212121599E-5</v>
+        <v>5.2112225372847546E-5</v>
       </c>
       <c r="W2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,W$1)</f>
-        <v>8.8571471228200954E-5</v>
+        <v>5.1048710569319682E-5</v>
       </c>
       <c r="X2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,X$1)</f>
-        <v>8.6726232244279874E-5</v>
+        <v>4.9985195765792252E-5</v>
       </c>
       <c r="Y2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,Y$1)</f>
-        <v>8.4880993260359229E-5</v>
+        <v>4.8921680962264822E-5</v>
       </c>
       <c r="Z2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,Z$1)</f>
-        <v>8.303575427643815E-5</v>
+        <v>4.7858166158737392E-5</v>
       </c>
       <c r="AA2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AA$1)</f>
-        <v>8.1190515292517505E-5</v>
+        <v>4.6794651355209962E-5</v>
       </c>
       <c r="AB2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AB$1)</f>
-        <v>7.9345276308596425E-5</v>
+        <v>4.5731136551682532E-5</v>
       </c>
       <c r="AC2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AC$1)</f>
-        <v>7.750003732467578E-5</v>
+        <v>4.4667621748155101E-5</v>
       </c>
       <c r="AD2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AD$1)</f>
-        <v>7.5654798340754701E-5</v>
+        <v>4.3604106944627238E-5</v>
       </c>
       <c r="AE2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AE$1)</f>
-        <v>7.3809559356834056E-5</v>
+        <v>4.2540592141099808E-5</v>
       </c>
       <c r="AF2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AF$1)</f>
-        <v>7.1964320372912977E-5</v>
+        <v>4.1477077337572377E-5</v>
       </c>
       <c r="AG2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AG$1)</f>
-        <v>7.0119081388992331E-5</v>
+        <v>4.0413562534044947E-5</v>
       </c>
       <c r="AH2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AH$1)</f>
-        <v>6.8273842405071686E-5</v>
+        <v>3.9350047730517517E-5</v>
       </c>
       <c r="AI2" s="11">
         <f>TREND('DoE Data'!$C$26:$D$26,'DoE Data'!$C$22:$D$22,AI$1)</f>
-        <v>6.6428603421150607E-5</v>
+        <v>3.8286532926990087E-5</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
@@ -5590,139 +7367,139 @@
       </c>
       <c r="B7" s="11">
         <f>B2</f>
-        <v>1.6730166787549267E-4</v>
+        <v>9.642534218649336E-5</v>
       </c>
       <c r="C7" s="11">
         <f t="shared" ref="C7:AI7" si="23">C2</f>
-        <v>1.6238103058503588E-4</v>
+        <v>9.3589302710419923E-5</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="23"/>
-        <v>1.5746039329458082E-4</v>
+        <v>9.0753263234346487E-5</v>
       </c>
       <c r="E7" s="11">
         <f t="shared" si="23"/>
-        <v>1.5253975600412577E-4</v>
+        <v>8.7917223758273051E-5</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="23"/>
-        <v>1.4761911871366898E-4</v>
+        <v>8.5081184282199615E-5</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" si="23"/>
-        <v>1.4269848142321392E-4</v>
+        <v>8.2245144806126179E-5</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="23"/>
-        <v>1.3777784413275887E-4</v>
+        <v>7.940910533005361E-5</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="23"/>
-        <v>1.3285720684230208E-4</v>
+        <v>7.6573065853980174E-5</v>
       </c>
       <c r="J7" s="11">
         <f t="shared" si="23"/>
-        <v>1.2793656955184703E-4</v>
+        <v>7.3737026377906738E-5</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="23"/>
-        <v>1.2301593226139197E-4</v>
+        <v>7.0900986901833302E-5</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="23"/>
-        <v>1.1809529497093518E-4</v>
+        <v>6.8064947425759866E-5</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="23"/>
-        <v>1.1317465768048013E-4</v>
+        <v>6.5228907949686429E-5</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="23"/>
-        <v>1.0825402039002507E-4</v>
+        <v>6.2392868473612993E-5</v>
       </c>
       <c r="O7" s="26">
         <f t="shared" si="23"/>
-        <v>1.0333338309957002E-4</v>
+        <v>5.9556828997540424E-5</v>
       </c>
       <c r="P7" s="11">
         <f t="shared" si="23"/>
-        <v>1.0148814411564677E-4</v>
+        <v>5.8493314194012561E-5</v>
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="23"/>
-        <v>9.9642905131726127E-5</v>
+        <v>5.7429799390484697E-5</v>
       </c>
       <c r="R7" s="11">
         <f t="shared" si="23"/>
-        <v>9.7797666147805048E-5</v>
+        <v>5.6366284586957267E-5</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="23"/>
-        <v>9.5952427163884402E-5</v>
+        <v>5.5302769783429837E-5</v>
       </c>
       <c r="T7" s="11">
         <f t="shared" si="23"/>
-        <v>9.4107188179963323E-5</v>
+        <v>5.4239254979902406E-5</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="23"/>
-        <v>9.2261949196042678E-5</v>
+        <v>5.3175740176374976E-5</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="23"/>
-        <v>9.0416710212121599E-5</v>
+        <v>5.2112225372847546E-5</v>
       </c>
       <c r="W7" s="11">
         <f t="shared" si="23"/>
-        <v>8.8571471228200954E-5</v>
+        <v>5.1048710569319682E-5</v>
       </c>
       <c r="X7" s="11">
         <f t="shared" si="23"/>
-        <v>8.6726232244279874E-5</v>
+        <v>4.9985195765792252E-5</v>
       </c>
       <c r="Y7" s="11">
         <f t="shared" si="23"/>
-        <v>8.4880993260359229E-5</v>
+        <v>4.8921680962264822E-5</v>
       </c>
       <c r="Z7" s="11">
         <f t="shared" si="23"/>
-        <v>8.303575427643815E-5</v>
+        <v>4.7858166158737392E-5</v>
       </c>
       <c r="AA7" s="11">
         <f t="shared" si="23"/>
-        <v>8.1190515292517505E-5</v>
+        <v>4.6794651355209962E-5</v>
       </c>
       <c r="AB7" s="11">
         <f t="shared" si="23"/>
-        <v>7.9345276308596425E-5</v>
+        <v>4.5731136551682532E-5</v>
       </c>
       <c r="AC7" s="11">
         <f t="shared" si="23"/>
-        <v>7.750003732467578E-5</v>
+        <v>4.4667621748155101E-5</v>
       </c>
       <c r="AD7" s="11">
         <f t="shared" si="23"/>
-        <v>7.5654798340754701E-5</v>
+        <v>4.3604106944627238E-5</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="23"/>
-        <v>7.3809559356834056E-5</v>
+        <v>4.2540592141099808E-5</v>
       </c>
       <c r="AF7" s="11">
         <f t="shared" si="23"/>
-        <v>7.1964320372912977E-5</v>
+        <v>4.1477077337572377E-5</v>
       </c>
       <c r="AG7" s="11">
         <f t="shared" si="23"/>
-        <v>7.0119081388992331E-5</v>
+        <v>4.0413562534044947E-5</v>
       </c>
       <c r="AH7" s="11">
         <f t="shared" si="23"/>
-        <v>6.8273842405071686E-5</v>
+        <v>3.9350047730517517E-5</v>
       </c>
       <c r="AI7" s="11">
         <f t="shared" si="23"/>
-        <v>6.6428603421150607E-5</v>
+        <v>3.8286532926990087E-5</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
@@ -5874,7 +7651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -5997,140 +7774,140 @@
         <v>7</v>
       </c>
       <c r="B2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,B$1)</f>
-        <v>8.3650833937745032E-6</v>
+        <f>HPEC!B2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>6.6469607059989103E-6</v>
       </c>
       <c r="C2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,C$1)</f>
-        <v>8.1190515292517938E-6</v>
+        <f>HPEC!C2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>6.4514618617048174E-6</v>
       </c>
       <c r="D2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,D$1)</f>
-        <v>7.8730196647289761E-6</v>
+        <f>HPEC!D2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>6.2559630174107245E-6</v>
       </c>
       <c r="E2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,E$1)</f>
-        <v>7.6269878002061583E-6</v>
+        <f>HPEC!E2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>6.0604641731166324E-6</v>
       </c>
       <c r="F2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,F$1)</f>
-        <v>7.3809559356834489E-6</v>
+        <f>HPEC!F2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>5.8649653288225395E-6</v>
       </c>
       <c r="G2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,G$1)</f>
-        <v>7.1349240711606312E-6</v>
+        <f>HPEC!G2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>5.6694664845284466E-6</v>
       </c>
       <c r="H2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,H$1)</f>
-        <v>6.8888922066378134E-6</v>
+        <f>HPEC!H2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>5.4739676402344138E-6</v>
       </c>
       <c r="I2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,I$1)</f>
-        <v>6.642860342115104E-6</v>
+        <f>HPEC!I2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>5.2784687959403217E-6</v>
       </c>
       <c r="J2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,J$1)</f>
-        <v>6.3968284775922863E-6</v>
+        <f>HPEC!J2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>5.0829699516462288E-6</v>
       </c>
       <c r="K2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,K$1)</f>
-        <v>6.1507966130694685E-6</v>
+        <f>HPEC!K2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.8874711073521359E-6</v>
       </c>
       <c r="L2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,L$1)</f>
-        <v>5.9047647485467591E-6</v>
+        <f>HPEC!L2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.6919722630580438E-6</v>
       </c>
       <c r="M2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,M$1)</f>
-        <v>5.6587328840239414E-6</v>
+        <f>HPEC!M2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.4964734187639509E-6</v>
       </c>
       <c r="N2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,N$1)</f>
-        <v>5.4127010195011236E-6</v>
+        <f>HPEC!N2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.3009745744698588E-6</v>
       </c>
       <c r="O2" s="11">
-        <f>TREND('DoE Data'!$B$29:$C$29,'DoE Data'!$B$22:$C$22,O$1)</f>
-        <v>5.1666691549784143E-6</v>
+        <f>HPEC!O2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.1054757301758252E-6</v>
       </c>
       <c r="P2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,P$1)</f>
-        <v>5.074407205782344E-6</v>
+        <f>HPEC!P2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>4.0321636635655183E-6</v>
       </c>
       <c r="Q2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,Q$1)</f>
-        <v>4.9821452565863009E-6</v>
+        <f>HPEC!Q2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.9588515969552114E-6</v>
       </c>
       <c r="R2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,R$1)</f>
-        <v>4.8898833073902578E-6</v>
+        <f>HPEC!R2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.8855395303449342E-6</v>
       </c>
       <c r="S2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,S$1)</f>
-        <v>4.7976213581942147E-6</v>
+        <f>HPEC!S2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.8122274637346565E-6</v>
       </c>
       <c r="T2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,T$1)</f>
-        <v>4.7053594089981716E-6</v>
+        <f>HPEC!T2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.7389153971243793E-6</v>
       </c>
       <c r="U2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,U$1)</f>
-        <v>4.6130974598021285E-6</v>
+        <f>HPEC!U2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.6656033305141021E-6</v>
       </c>
       <c r="V2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,V$1)</f>
-        <v>4.5208355106060854E-6</v>
+        <f>HPEC!V2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.5922912639038249E-6</v>
       </c>
       <c r="W2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,W$1)</f>
-        <v>4.4285735614100423E-6</v>
+        <f>HPEC!W2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.5189791972935176E-6</v>
       </c>
       <c r="X2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,X$1)</f>
-        <v>4.3363116122139991E-6</v>
+        <f>HPEC!X2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.4456671306832404E-6</v>
       </c>
       <c r="Y2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,Y$1)</f>
-        <v>4.244049663017956E-6</v>
+        <f>HPEC!Y2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.3723550640729631E-6</v>
       </c>
       <c r="Z2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,Z$1)</f>
-        <v>4.1517877138219129E-6</v>
+        <f>HPEC!Z2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.2990429974626859E-6</v>
       </c>
       <c r="AA2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AA$1)</f>
-        <v>4.0595257646258698E-6</v>
+        <f>HPEC!AA2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.2257309308524087E-6</v>
       </c>
       <c r="AB2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AB$1)</f>
-        <v>3.9672638154298267E-6</v>
+        <f>HPEC!AB2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.1524188642421315E-6</v>
       </c>
       <c r="AC2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AC$1)</f>
-        <v>3.8750018662337836E-6</v>
+        <f>HPEC!AC2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.0791067976318543E-6</v>
       </c>
       <c r="AD2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AD$1)</f>
-        <v>3.7827399170377405E-6</v>
+        <f>HPEC!AD2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>3.005794731021547E-6</v>
       </c>
       <c r="AE2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AE$1)</f>
-        <v>3.6904779678416974E-6</v>
+        <f>HPEC!AE2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>2.9324826644112697E-6</v>
       </c>
       <c r="AF2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AF$1)</f>
-        <v>3.5982160186456542E-6</v>
+        <f>HPEC!AF2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>2.8591705978009925E-6</v>
       </c>
       <c r="AG2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AG$1)</f>
-        <v>3.5059540694496111E-6</v>
+        <f>HPEC!AG2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>2.7858585311907153E-6</v>
       </c>
       <c r="AH2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AH$1)</f>
-        <v>3.413692120253568E-6</v>
+        <f>HPEC!AH2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>2.7125464645804381E-6</v>
       </c>
       <c r="AI2" s="11">
-        <f>TREND('DoE Data'!$C$29:$D$29,'DoE Data'!$C$22:$D$22,AI$1)</f>
-        <v>3.3214301710575249E-6</v>
+        <f>HPEC!AI2*('OM Split'!$B$20+'OM Split'!$B$21)</f>
+        <v>2.6392343979701609E-6</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
@@ -6138,140 +7915,140 @@
         <v>16</v>
       </c>
       <c r="B3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="C3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="D3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="E3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="F3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="G3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="H3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="I3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="J3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="K3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="L3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="M3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="N3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="O3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="P3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Q3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="R3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="S3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="T3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="U3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="V3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="W3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="X3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Y3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Z3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AA3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AB3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AC3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AD3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AE3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AF3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AG3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AH3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AI3" s="11">
-        <f>'Reformer data'!$B$36</f>
-        <v>1.3705922676579926E-6</v>
+        <f>'OM Split'!$B$13</f>
+        <v>6.9414023552214001E-7</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
@@ -6279,140 +8056,140 @@
         <v>19</v>
       </c>
       <c r="B4" s="11">
-        <f>B3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="C4" s="11">
-        <f>C3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="D4" s="11">
-        <f>D3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="E4" s="11">
-        <f>E3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="F4" s="11">
-        <f>F3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="G4" s="11">
-        <f>G3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="H4" s="11">
-        <f>H3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="I4" s="11">
-        <f>I3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="J4" s="11">
-        <f>J3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="K4" s="11">
-        <f>K3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="L4" s="11">
-        <f>L3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="M4" s="11">
-        <f>M3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="N4" s="11">
-        <f>N3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="O4" s="11">
-        <f>O3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="P4" s="11">
-        <f>P3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Q4" s="11">
-        <f>Q3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="R4" s="11">
-        <f>R3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="S4" s="11">
-        <f>S3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="T4" s="11">
-        <f>T3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="U4" s="11">
-        <f>U3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="V4" s="11">
-        <f>V3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="W4" s="11">
-        <f>W3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="X4" s="11">
-        <f>X3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Y4" s="11">
-        <f>Y3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Z4" s="11">
-        <f>Z3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AA4" s="11">
-        <f>AA3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AB4" s="11">
-        <f>AB3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AC4" s="11">
-        <f>AC3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AD4" s="11">
-        <f>AD3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AE4" s="11">
-        <f>AE3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AF4" s="11">
-        <f>AF3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AG4" s="11">
-        <f>AG3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AH4" s="11">
-        <f>AH3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AI4" s="11">
-        <f>AI3*'IEA Data'!$D$10/'IEA Data'!$D$6</f>
-        <v>4.021408082029495E-6</v>
+        <f>'OM Split'!$C$13</f>
+        <v>5.3746768810269592E-6</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
@@ -6421,139 +8198,139 @@
       </c>
       <c r="B5" s="11">
         <f>B4</f>
-        <v>4.021408082029495E-6</v>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="C5" s="11">
-        <f t="shared" ref="C5:AI5" si="0">C4</f>
-        <v>4.021408082029495E-6</v>
+        <f>C4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="D5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>D4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>E4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="F5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>F4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="G5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>G4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="H5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>H4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="I5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>I4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="J5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>J4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="K5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>K4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="L5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>L4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="M5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>M4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="N5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>N4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="O5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>O4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>P4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>Q4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>R4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="S5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>S4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="T5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>T4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="U5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>U4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="V5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>V4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="W5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>W4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="X5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>X4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Y5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>Y4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="Z5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>Z4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AA5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AA4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AB5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AB4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AC5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AC4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AD5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AD4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AE5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AE4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AF5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AF4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AG5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AG4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AH5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AH4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
       <c r="AI5" s="11">
-        <f t="shared" si="0"/>
-        <v>4.021408082029495E-6</v>
+        <f>AI4</f>
+        <v>5.3746768810269592E-6</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
@@ -6562,139 +8339,139 @@
       </c>
       <c r="B6" s="11">
         <f>B3*0.85</f>
-        <v>1.1650034275092937E-6</v>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="C6" s="11">
-        <f t="shared" ref="C6:AI6" si="1">C3*0.85</f>
-        <v>1.1650034275092937E-6</v>
+        <f>C3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="D6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>D3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>E3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="F6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>F3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="G6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>G3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="H6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>H3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="I6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>I3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="J6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>J3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="K6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>K3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="L6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>L3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>M3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="N6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>N3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="O6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>O3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="P6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>P3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="Q6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>Q3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="R6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>R3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="S6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>S3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="T6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>T3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="U6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>U3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="V6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>V3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="W6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>W3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="X6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>X3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="Y6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>Y3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="Z6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>Z3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AA6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AA3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AB6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AB3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AC6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AC3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AD6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AD3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AE6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AE3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AF6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AF3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AG6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AG3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AH6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AH3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
       <c r="AI6" s="11">
-        <f t="shared" si="1"/>
-        <v>1.1650034275092937E-6</v>
+        <f>AI3*0.85</f>
+        <v>5.9001920019381897E-7</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
@@ -6702,140 +8479,140 @@
         <v>63</v>
       </c>
       <c r="B7" s="11">
-        <f>B2</f>
-        <v>8.3650833937745032E-6</v>
+        <f>HPEC!B7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>6.3550334415641373E-6</v>
       </c>
       <c r="C7" s="11">
-        <f t="shared" ref="C7:AI7" si="2">C2</f>
-        <v>8.1190515292517938E-6</v>
+        <f>HPEC!C7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>6.1681206932828326E-6</v>
       </c>
       <c r="D7" s="11">
-        <f t="shared" si="2"/>
-        <v>7.8730196647289761E-6</v>
+        <f>HPEC!D7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.981207945001528E-6</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="2"/>
-        <v>7.6269878002061583E-6</v>
+        <f>HPEC!E7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.7942951967202225E-6</v>
       </c>
       <c r="F7" s="11">
-        <f t="shared" si="2"/>
-        <v>7.3809559356834489E-6</v>
+        <f>HPEC!F7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.6073824484389178E-6</v>
       </c>
       <c r="G7" s="11">
-        <f t="shared" si="2"/>
-        <v>7.1349240711606312E-6</v>
+        <f>HPEC!G7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.4204697001576132E-6</v>
       </c>
       <c r="H7" s="11">
-        <f t="shared" si="2"/>
-        <v>6.8888922066378134E-6</v>
+        <f>HPEC!H7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.2335569518763652E-6</v>
       </c>
       <c r="I7" s="11">
-        <f t="shared" si="2"/>
-        <v>6.642860342115104E-6</v>
+        <f>HPEC!I7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>5.0466442035950606E-6</v>
       </c>
       <c r="J7" s="11">
-        <f t="shared" si="2"/>
-        <v>6.3968284775922863E-6</v>
+        <f>HPEC!J7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>4.8597314553137551E-6</v>
       </c>
       <c r="K7" s="11">
-        <f t="shared" si="2"/>
-        <v>6.1507966130694685E-6</v>
+        <f>HPEC!K7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>4.6728187070324504E-6</v>
       </c>
       <c r="L7" s="11">
-        <f t="shared" si="2"/>
-        <v>5.9047647485467591E-6</v>
+        <f>HPEC!L7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>4.4859059587511458E-6</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="2"/>
-        <v>5.6587328840239414E-6</v>
+        <f>HPEC!M7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>4.2989932104698411E-6</v>
       </c>
       <c r="N7" s="11">
-        <f t="shared" si="2"/>
-        <v>5.4127010195011236E-6</v>
+        <f>HPEC!N7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>4.1120804621885356E-6</v>
       </c>
       <c r="O7" s="11">
-        <f t="shared" si="2"/>
-        <v>5.1666691549784143E-6</v>
+        <f>HPEC!O7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.9251677139072885E-6</v>
       </c>
       <c r="P7" s="11">
-        <f t="shared" si="2"/>
-        <v>5.074407205782344E-6</v>
+        <f>HPEC!P7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.8550754333017774E-6</v>
       </c>
       <c r="Q7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.9821452565863009E-6</v>
+        <f>HPEC!Q7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.7849831526962666E-6</v>
       </c>
       <c r="R7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.8898833073902578E-6</v>
+        <f>HPEC!R7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.7148908720907843E-6</v>
       </c>
       <c r="S7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.7976213581942147E-6</v>
+        <f>HPEC!S7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.6447985914853023E-6</v>
       </c>
       <c r="T7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.7053594089981716E-6</v>
+        <f>HPEC!T7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.57470631087982E-6</v>
       </c>
       <c r="U7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.6130974598021285E-6</v>
+        <f>HPEC!U7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.504614030274338E-6</v>
       </c>
       <c r="V7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.5208355106060854E-6</v>
+        <f>HPEC!V7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.4345217496688557E-6</v>
       </c>
       <c r="W7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.4285735614100423E-6</v>
+        <f>HPEC!W7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.3644294690633449E-6</v>
       </c>
       <c r="X7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.3363116122139991E-6</v>
+        <f>HPEC!X7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.294337188457863E-6</v>
       </c>
       <c r="Y7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.244049663017956E-6</v>
+        <f>HPEC!Y7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.2242449078523806E-6</v>
       </c>
       <c r="Z7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.1517877138219129E-6</v>
+        <f>HPEC!Z7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.1541526272468983E-6</v>
       </c>
       <c r="AA7" s="11">
-        <f t="shared" si="2"/>
-        <v>4.0595257646258698E-6</v>
+        <f>HPEC!AA7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.0840603466414163E-6</v>
       </c>
       <c r="AB7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.9672638154298267E-6</v>
+        <f>HPEC!AB7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>3.013968066035934E-6</v>
       </c>
       <c r="AC7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.8750018662337836E-6</v>
+        <f>HPEC!AC7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.943875785430452E-6</v>
       </c>
       <c r="AD7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.7827399170377405E-6</v>
+        <f>HPEC!AD7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.8737835048249413E-6</v>
       </c>
       <c r="AE7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.6904779678416974E-6</v>
+        <f>HPEC!AE7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.8036912242194589E-6</v>
       </c>
       <c r="AF7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.5982160186456542E-6</v>
+        <f>HPEC!AF7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.7335989436139765E-6</v>
       </c>
       <c r="AG7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.5059540694496111E-6</v>
+        <f>HPEC!AG7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.6635066630084946E-6</v>
       </c>
       <c r="AH7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.413692120253568E-6</v>
+        <f>HPEC!AH7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.5934143824030122E-6</v>
       </c>
       <c r="AI7" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3214301710575249E-6</v>
+        <f>HPEC!AI7*('OM Split'!$C$20+'OM Split'!$C$21)</f>
+        <v>2.5233221017975303E-6</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
@@ -6844,139 +8621,139 @@
       </c>
       <c r="B8" s="11">
         <f>B3</f>
-        <v>1.3705922676579926E-6</v>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:AI8" si="3">C3</f>
-        <v>1.3705922676579926E-6</v>
+        <f>C3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="D8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>D3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>E3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="F8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>F3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="G8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>G3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="H8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>H3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="I8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>I3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="J8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>J3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="K8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>K3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="L8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>L3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="M8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>M3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="N8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>N3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="O8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>O3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="P8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>P3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Q8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>Q3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="R8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>R3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="S8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>S3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="T8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>T3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="U8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>U3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="V8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>V3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="W8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>W3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="X8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>X3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Y8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>Y3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="Z8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>Z3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AA8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AA3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AB8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AB3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AC8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AC3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AD8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AD3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AE8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AE3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AF8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AF3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AG8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AG3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AH8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AH3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
       <c r="AI8" s="11">
-        <f t="shared" si="3"/>
-        <v>1.3705922676579926E-6</v>
+        <f>AI3</f>
+        <v>6.9414023552214001E-7</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
@@ -7002,6 +8779,87 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{723437F8-2B00-417E-A96B-7379FC337CBB}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <f>'OM Split'!$B$22</f>
+        <v>0.27466592288209951</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <f>'OM Split'!$B$14</f>
+        <v>0.40951004310489969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <f>'OM Split'!$C$14</f>
+        <v>0.46469109050688168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <f>'OM Split'!$C$14</f>
+        <v>0.46469109050688168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6">
+        <f>'OM Split'!$B$14</f>
+        <v>0.40951004310489969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <f>'OM Split'!$C$22</f>
+        <v>0.24134669728220506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <f>'OM Split'!$B$14</f>
+        <v>0.40951004310489969</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
